--- a/output/pdf_financials_xlsx/VIS.xlsx
+++ b/output/pdf_financials_xlsx/VIS.xlsx
@@ -4628,25 +4628,25 @@
         <v>0.988348</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.988348</v>
+        <v>1.166025</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.988348</v>
+        <v>1.235317</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>1.02383</v>
+        <v>1.539192</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.041792</v>
+        <v>1.908678</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1.041792</v>
+        <v>1.908678</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>1.908678</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>1.908678</v>
+        <v>2.524124</v>
       </c>
     </row>
     <row r="93">
@@ -7975,7 +7975,11 @@
           <t>WARRANT RESERVE (Note 14)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10613,7 +10617,11 @@
           <t>WARRANT RESERVE (Note 13)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VIS.xlsx
+++ b/output/pdf_financials_xlsx/VIS.xlsx
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.028032</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004049</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003835</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -2238,19 +2238,19 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.042427</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.013857</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.017051</v>
       </c>
     </row>
     <row r="35">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.028032</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.004049</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003835</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -2318,19 +2318,19 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.042427</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.013857</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.017051</v>
       </c>
     </row>
     <row r="37">
@@ -2780,13 +2780,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.164945</v>
+        <v>0.136913</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.129207</v>
+        <v>0.125158</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.038968</v>
+        <v>0.035133</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.014458</v>
@@ -2798,19 +2798,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.056717</v>
+        <v>0.01429</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.013466</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.019942</v>
+        <v>0.006085</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.017051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">

--- a/output/pdf_financials_xlsx/VIS.xlsx
+++ b/output/pdf_financials_xlsx/VIS.xlsx
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.003067</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.003835</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.00497</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.003567</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.003567</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.001962</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -19876,7 +19876,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VIS.xlsx
+++ b/output/pdf_financials_xlsx/VIS.xlsx
@@ -22042,7 +22042,11 @@
           <t>Private Placement</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
